--- a/output/graficos_regionales_piramide/plot_comunal_piramide_2022_biobio.xlsx
+++ b/output/graficos_regionales_piramide/plot_comunal_piramide_2022_biobio.xlsx
@@ -141,13 +141,13 @@
     <t xml:space="preserve">Curanilahue</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Tirúa</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Antuco</t>
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30 15:44</t>
+    <t xml:space="preserve">2026-10-05 21:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
